--- a/Result/profitability/2015.xlsx
+++ b/Result/profitability/2015.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.21</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11125</v>
+        <v>1.19625</v>
       </c>
       <c r="N2" t="n">
-        <v>12.34125</v>
+        <v>12.835</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.45125</v>
+        <v>1.495</v>
       </c>
       <c r="N3" t="n">
-        <v>14.08625</v>
+        <v>14.3075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.29</v>
+        <v>1.37125</v>
       </c>
       <c r="N4" t="n">
-        <v>13.2525</v>
+        <v>13.4975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0.93</v>
+        <v>0.96875</v>
       </c>
       <c r="N5" t="n">
-        <v>8.335000000000001</v>
+        <v>8.5025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.9375</v>
       </c>
       <c r="N6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.23875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.81875</v>
+        <v>0.88375</v>
       </c>
       <c r="N7" t="n">
-        <v>9.04875</v>
+        <v>9.185</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0.785</v>
+        <v>0.85375</v>
       </c>
       <c r="N8" t="n">
-        <v>8.7775</v>
+        <v>8.768750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.3075</v>
       </c>
       <c r="N11" t="n">
-        <v>6.867500000000001</v>
+        <v>6.8675</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.44125</v>
       </c>
       <c r="N12" t="n">
-        <v>7.828750000000001</v>
+        <v>7.82875</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7587</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6621</v>
+      </c>
+      <c r="E75" t="n">
+        <v>966</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>734</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>255</v>
+      </c>
+      <c r="J75" t="n">
+        <v>988</v>
+      </c>
+      <c r="K75" t="n">
+        <v>847</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.44625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6043956043956042</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.07000000000000028</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005464480874316946</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2695652173913043</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1175438596491227</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
